--- a/src/fixtures/sample/gstr2b-2026-04.xlsx
+++ b/src/fixtures/sample/gstr2b-2026-04.xlsx
@@ -470,25 +470,25 @@
         <v>Mahesh Steel Traders</v>
       </c>
       <c r="C6" t="str">
-        <v>S01/2026/052</v>
+        <v>S01/2026/041</v>
       </c>
       <c r="D6" t="str">
-        <v>08/02/2026</v>
+        <v>19/01/2026</v>
       </c>
       <c r="E6">
-        <v>559320</v>
+        <v>572300</v>
       </c>
       <c r="F6">
-        <v>474000</v>
+        <v>485000</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>42660</v>
+        <v>43650</v>
       </c>
       <c r="I6">
-        <v>42660</v>
+        <v>43650</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -497,7 +497,7 @@
         <v>2026-05</v>
       </c>
       <c r="L6" t="str">
-        <v>19/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="M6" t="str">
         <v>Yes</v>
@@ -511,31 +511,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>27AAPFM4821K1ZV</v>
+        <v>27AABFS9034J1ZY</v>
       </c>
       <c r="B7" t="str">
-        <v>Mahesh Steel Traders</v>
+        <v>Surya Electricals</v>
       </c>
       <c r="C7" t="str">
-        <v>S01/2026/072</v>
+        <v>SE 71</v>
       </c>
       <c r="D7" t="str">
         <v>23/04/2026</v>
       </c>
       <c r="E7">
-        <v>553420</v>
+        <v>164020</v>
       </c>
       <c r="F7">
-        <v>469000</v>
+        <v>139000</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>42210</v>
+        <v>12510</v>
       </c>
       <c r="I7">
-        <v>42210</v>
+        <v>12510</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>2026-05</v>
       </c>
       <c r="L7" t="str">
-        <v>14/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
@@ -558,31 +558,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>27AAPFM4821K1ZV</v>
+        <v>27AABFS9034J1ZY</v>
       </c>
       <c r="B8" t="str">
-        <v>Mahesh Steel Traders</v>
+        <v>Surya Electricals</v>
       </c>
       <c r="C8" t="str">
-        <v>S01/2026/073</v>
+        <v>SE 71</v>
       </c>
       <c r="D8" t="str">
-        <v>07/04/2026</v>
+        <v>09/04/2026</v>
       </c>
       <c r="E8">
-        <v>556960</v>
+        <v>171100</v>
       </c>
       <c r="F8">
-        <v>472000</v>
+        <v>145000</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>42480</v>
+        <v>13050</v>
       </c>
       <c r="I8">
-        <v>42480</v>
+        <v>13050</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>2026-05</v>
       </c>
       <c r="L8" t="str">
-        <v>11/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
@@ -605,31 +605,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>27AABFS9034J1ZY</v>
+        <v>27AAJFN2276C1ZC</v>
       </c>
       <c r="B9" t="str">
-        <v>Surya Electricals</v>
+        <v>Nilkanth Traders</v>
       </c>
       <c r="C9" t="str">
-        <v>SE 71</v>
+        <v>S07/2026/071</v>
       </c>
       <c r="D9" t="str">
-        <v>17/04/2026</v>
+        <v>19/04/2026</v>
       </c>
       <c r="E9">
-        <v>167560</v>
+        <v>250160</v>
       </c>
       <c r="F9">
-        <v>142000</v>
+        <v>212000</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>12780</v>
+        <v>19080</v>
       </c>
       <c r="I9">
-        <v>12780</v>
+        <v>19080</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>2026-05</v>
       </c>
       <c r="L9" t="str">
-        <v>08/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
@@ -652,31 +652,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>27AABFS9034J1ZY</v>
+        <v>27AAJFN2276C1ZC</v>
       </c>
       <c r="B10" t="str">
-        <v>Surya Electricals</v>
+        <v>Nilkanth Traders</v>
       </c>
       <c r="C10" t="str">
-        <v>SE 71</v>
+        <v>S07/2026/072</v>
       </c>
       <c r="D10" t="str">
-        <v>11/04/2026</v>
+        <v>05/04/2026</v>
       </c>
       <c r="E10">
-        <v>179360</v>
+        <v>251340</v>
       </c>
       <c r="F10">
-        <v>152000</v>
+        <v>213000</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>13680</v>
+        <v>19170</v>
       </c>
       <c r="I10">
-        <v>13680</v>
+        <v>19170</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>2026-05</v>
       </c>
       <c r="L10" t="str">
-        <v>12/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="M10" t="str">
         <v>Yes</v>
@@ -699,31 +699,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>27AAJFN2276C1ZC</v>
+        <v>24AAECR8890P1ZI</v>
       </c>
       <c r="B11" t="str">
-        <v>Nilkanth Traders</v>
+        <v>Ratna Chemicals</v>
       </c>
       <c r="C11" t="str">
-        <v>S07/2026/071</v>
+        <v>S08/2026/071</v>
       </c>
       <c r="D11" t="str">
-        <v>10/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="E11">
-        <v>252520</v>
+        <v>215940</v>
       </c>
       <c r="F11">
-        <v>214000</v>
+        <v>183000</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>32940</v>
       </c>
       <c r="H11">
-        <v>19260</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>19260</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>2026-05</v>
       </c>
       <c r="L11" t="str">
-        <v>11/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
@@ -746,31 +746,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>27AAJFN2276C1ZC</v>
+        <v>24AAECR8890P1ZI</v>
       </c>
       <c r="B12" t="str">
-        <v>Nilkanth Traders</v>
+        <v>Ratna Chemicals</v>
       </c>
       <c r="C12" t="str">
-        <v>S07/2026/072</v>
+        <v>S08/2026/072</v>
       </c>
       <c r="D12" t="str">
-        <v>23/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="E12">
-        <v>236000</v>
+        <v>219480</v>
       </c>
       <c r="F12">
-        <v>200000</v>
+        <v>186000</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>33480</v>
       </c>
       <c r="H12">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -793,31 +793,31 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24AAECR8890P1ZI</v>
+        <v>27AAACM6543N1Z3</v>
       </c>
       <c r="B13" t="str">
-        <v>Ratna Chemicals</v>
+        <v>Metro Motors</v>
       </c>
       <c r="C13" t="str">
-        <v>S08/2026/071</v>
+        <v>S09/2026/071</v>
       </c>
       <c r="D13" t="str">
-        <v>18/04/2026</v>
+        <v>03/04/2026</v>
       </c>
       <c r="E13">
-        <v>206500</v>
+        <v>1059640</v>
       </c>
       <c r="F13">
-        <v>175000</v>
+        <v>898000</v>
       </c>
       <c r="G13">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>80820</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>80820</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -826,13 +826,13 @@
         <v>2026-05</v>
       </c>
       <c r="L13" t="str">
-        <v>15/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="M13" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>ITC unavailable - blocked credit</v>
       </c>
       <c r="O13" t="str">
         <v>N</v>
@@ -840,25 +840,25 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>24AAECR8890P1ZI</v>
+        <v>27AAFCV4412Q2ZU</v>
       </c>
       <c r="B14" t="str">
-        <v>Ratna Chemicals</v>
+        <v>Vindhya Alloys</v>
       </c>
       <c r="C14" t="str">
-        <v>S08/2026/072</v>
+        <v>S10/2026/071</v>
       </c>
       <c r="D14" t="str">
-        <v>20/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="E14">
-        <v>212400</v>
+        <v>320960</v>
       </c>
       <c r="F14">
-        <v>180000</v>
+        <v>272000</v>
       </c>
       <c r="G14">
-        <v>32400</v>
+        <v>48960</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -887,31 +887,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>27AAACM6543N1Z3</v>
+        <v>27AAFCV4412Q2ZU</v>
       </c>
       <c r="B15" t="str">
-        <v>Metro Motors</v>
+        <v>Vindhya Alloys</v>
       </c>
       <c r="C15" t="str">
-        <v>S09/2026/071</v>
+        <v>S10/2026/072</v>
       </c>
       <c r="D15" t="str">
-        <v>16/04/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="E15">
-        <v>1058460</v>
+        <v>304440</v>
       </c>
       <c r="F15">
-        <v>897000</v>
+        <v>258000</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>46440</v>
       </c>
       <c r="H15">
-        <v>80730</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>80730</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -920,13 +920,13 @@
         <v>2026-05</v>
       </c>
       <c r="L15" t="str">
-        <v>15/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="M15" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N15" t="str">
-        <v>ITC unavailable - blocked credit</v>
+        <v/>
       </c>
       <c r="O15" t="str">
         <v>N</v>
@@ -934,31 +934,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>27AAFCV4412Q2ZU</v>
+        <v>27AAHFS1129D1ZH</v>
       </c>
       <c r="B16" t="str">
-        <v>Vindhya Alloys</v>
+        <v>Sahyadri Logistics</v>
       </c>
       <c r="C16" t="str">
-        <v>S10/2026/071</v>
+        <v>S11/2026/071</v>
       </c>
       <c r="D16" t="str">
-        <v>19/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="E16">
-        <v>304440</v>
+        <v>95580</v>
       </c>
       <c r="F16">
-        <v>258000</v>
+        <v>81000</v>
       </c>
       <c r="G16">
-        <v>46440</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>7290</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>7290</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>2026-05</v>
       </c>
       <c r="L16" t="str">
-        <v>15/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="M16" t="str">
         <v>Yes</v>
@@ -981,31 +981,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>27AAFCV4412Q2ZU</v>
+        <v>27AAHFS1129D1ZH</v>
       </c>
       <c r="B17" t="str">
-        <v>Vindhya Alloys</v>
+        <v>Sahyadri Logistics</v>
       </c>
       <c r="C17" t="str">
-        <v>S10/2026/072</v>
+        <v>S11/2026/072</v>
       </c>
       <c r="D17" t="str">
-        <v>16/04/2026</v>
+        <v>06/04/2026</v>
       </c>
       <c r="E17">
-        <v>306800</v>
+        <v>94400</v>
       </c>
       <c r="F17">
-        <v>260000</v>
+        <v>80000</v>
       </c>
       <c r="G17">
-        <v>46800</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>2026-05</v>
       </c>
       <c r="L17" t="str">
-        <v>15/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="M17" t="str">
         <v>Yes</v>
@@ -1028,31 +1028,31 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>27AAHFS1129D1ZH</v>
+        <v>27AAFCB2210G1Z8</v>
       </c>
       <c r="B18" t="str">
-        <v>Sahyadri Logistics</v>
+        <v>Bharat Office Supplies</v>
       </c>
       <c r="C18" t="str">
-        <v>S11/2026/071</v>
+        <v>S12/2026/071</v>
       </c>
       <c r="D18" t="str">
-        <v>07/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="E18">
-        <v>89680</v>
+        <v>197060</v>
       </c>
       <c r="F18">
-        <v>76000</v>
+        <v>167000</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>6840</v>
+        <v>15030</v>
       </c>
       <c r="I18">
-        <v>6840</v>
+        <v>15030</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1075,31 +1075,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>27AAHFS1129D1ZH</v>
+        <v>27AAFCB2210G1Z8</v>
       </c>
       <c r="B19" t="str">
-        <v>Sahyadri Logistics</v>
+        <v>Bharat Office Supplies</v>
       </c>
       <c r="C19" t="str">
-        <v>S11/2026/072</v>
+        <v>S12/2026/072</v>
       </c>
       <c r="D19" t="str">
-        <v>11/04/2026</v>
+        <v>14/04/2026</v>
       </c>
       <c r="E19">
-        <v>106200</v>
+        <v>177000</v>
       </c>
       <c r="F19">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>8100</v>
+        <v>13500</v>
       </c>
       <c r="I19">
-        <v>8100</v>
+        <v>13500</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>2026-05</v>
       </c>
       <c r="L19" t="str">
-        <v>08/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="M19" t="str">
         <v>Yes</v>
@@ -1122,31 +1122,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>27AAFCB2210G1Z8</v>
+        <v>27AAGFK5561R1ZL</v>
       </c>
       <c r="B20" t="str">
-        <v>Bharat Office Supplies</v>
+        <v>Konkan Hardware</v>
       </c>
       <c r="C20" t="str">
-        <v>S12/2026/062</v>
+        <v>S13/2026/071</v>
       </c>
       <c r="D20" t="str">
-        <v>16/03/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="E20">
-        <v>205320</v>
+        <v>74340</v>
       </c>
       <c r="F20">
-        <v>174000</v>
+        <v>63000</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>15660</v>
+        <v>5670</v>
       </c>
       <c r="I20">
-        <v>15660</v>
+        <v>5670</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>2026-05</v>
       </c>
       <c r="L20" t="str">
-        <v>14/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="M20" t="str">
         <v>Yes</v>
@@ -1169,31 +1169,31 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>27AAFCB2210G1Z8</v>
+        <v>24AAACT3398E1ZE</v>
       </c>
       <c r="B21" t="str">
-        <v>Bharat Office Supplies</v>
+        <v>Trident Paper Mills</v>
       </c>
       <c r="C21" t="str">
-        <v>S12/2026/071</v>
+        <v>S14/2026/071</v>
       </c>
       <c r="D21" t="str">
-        <v>21/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="E21">
-        <v>188800</v>
+        <v>156940</v>
       </c>
       <c r="F21">
-        <v>160000</v>
+        <v>133000</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>23940</v>
       </c>
       <c r="H21">
-        <v>14400</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>14400</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>2026-05</v>
       </c>
       <c r="L21" t="str">
-        <v>10/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="M21" t="str">
         <v>Yes</v>
@@ -1216,31 +1216,31 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>27AAFCB2210G1Z8</v>
+        <v>33AAJFL7745T1ZE</v>
       </c>
       <c r="B22" t="str">
-        <v>Bharat Office Supplies</v>
+        <v>Lakshmi Fasteners</v>
       </c>
       <c r="C22" t="str">
-        <v>S12/2026/072</v>
+        <v>S15/2026/071</v>
       </c>
       <c r="D22" t="str">
-        <v>14/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="E22">
-        <v>194700</v>
+        <v>31860</v>
       </c>
       <c r="F22">
-        <v>165000</v>
+        <v>27000</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>4860</v>
       </c>
       <c r="H22">
-        <v>14850</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>14850</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>2026-05</v>
       </c>
       <c r="L22" t="str">
-        <v>16/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="M22" t="str">
         <v>Yes</v>
@@ -1263,31 +1263,31 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>27AAGFK5561R1ZL</v>
+        <v>33AAJFL7745T1ZE</v>
       </c>
       <c r="B23" t="str">
-        <v>Konkan Hardware</v>
+        <v>Lakshmi Fasteners</v>
       </c>
       <c r="C23" t="str">
-        <v>S13/2026/071</v>
+        <v>S15/2026/072</v>
       </c>
       <c r="D23" t="str">
-        <v>17/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="E23">
-        <v>73160</v>
+        <v>48380</v>
       </c>
       <c r="F23">
-        <v>62000</v>
+        <v>41000</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>7380</v>
       </c>
       <c r="H23">
-        <v>5580</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>5580</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>2026-05</v>
       </c>
       <c r="L23" t="str">
-        <v>11/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="M23" t="str">
         <v>Yes</v>
@@ -1316,19 +1316,19 @@
         <v>Lakshmi Fasteners</v>
       </c>
       <c r="C24" t="str">
-        <v>S15/2026/071</v>
+        <v>S15/2026/073</v>
       </c>
       <c r="D24" t="str">
         <v>16/04/2026</v>
       </c>
       <c r="E24">
-        <v>41300</v>
+        <v>56640</v>
       </c>
       <c r="F24">
-        <v>35000</v>
+        <v>48000</v>
       </c>
       <c r="G24">
-        <v>6300</v>
+        <v>8640</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>2026-05</v>
       </c>
       <c r="L24" t="str">
-        <v>16/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="M24" t="str">
         <v>Yes</v>
@@ -1357,25 +1357,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>33AAJFL7745T1ZE</v>
+        <v>29AAECO9912W1Z8</v>
       </c>
       <c r="B25" t="str">
-        <v>Lakshmi Fasteners</v>
+        <v>Orion Software Services</v>
       </c>
       <c r="C25" t="str">
-        <v>S15/2026/072</v>
+        <v>S16/2026/071</v>
       </c>
       <c r="D25" t="str">
-        <v>08/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="E25">
-        <v>46020</v>
+        <v>76700</v>
       </c>
       <c r="F25">
-        <v>39000</v>
+        <v>65000</v>
       </c>
       <c r="G25">
-        <v>7020</v>
+        <v>11700</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>2026-05</v>
       </c>
       <c r="L25" t="str">
-        <v>16/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="M25" t="str">
         <v>Yes</v>
@@ -1404,25 +1404,25 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>33AAJFL7745T1ZE</v>
+        <v>29AAECO9912W1Z8</v>
       </c>
       <c r="B26" t="str">
-        <v>Lakshmi Fasteners</v>
+        <v>Orion Software Services</v>
       </c>
       <c r="C26" t="str">
-        <v>S15/2026/073</v>
+        <v>S16/2026/072</v>
       </c>
       <c r="D26" t="str">
-        <v>17/04/2026</v>
+        <v>05/04/2026</v>
       </c>
       <c r="E26">
-        <v>49560</v>
+        <v>56640</v>
       </c>
       <c r="F26">
-        <v>42000</v>
+        <v>48000</v>
       </c>
       <c r="G26">
-        <v>7560</v>
+        <v>8640</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1437,7 +1437,7 @@
         <v>2026-05</v>
       </c>
       <c r="L26" t="str">
-        <v>13/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="M26" t="str">
         <v>Yes</v>
@@ -1451,25 +1451,25 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>29AAECO9912W1Z8</v>
+        <v>09AAHFG4423Y1ZH</v>
       </c>
       <c r="B27" t="str">
-        <v>Orion Software Services</v>
+        <v>Ganga Textiles</v>
       </c>
       <c r="C27" t="str">
-        <v>S16/2026/071</v>
+        <v>S17/2026/071</v>
       </c>
       <c r="D27" t="str">
-        <v>07/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="E27">
-        <v>79060</v>
+        <v>67260</v>
       </c>
       <c r="F27">
-        <v>67000</v>
+        <v>57000</v>
       </c>
       <c r="G27">
-        <v>12060</v>
+        <v>10260</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1484,7 +1484,7 @@
         <v>2026-05</v>
       </c>
       <c r="L27" t="str">
-        <v>16/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="M27" t="str">
         <v>Yes</v>
@@ -1498,31 +1498,31 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>29AAECO9912W1Z8</v>
+        <v>27AAKFP6678U1ZU</v>
       </c>
       <c r="B28" t="str">
-        <v>Orion Software Services</v>
+        <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C28" t="str">
-        <v>S16/2026/072</v>
+        <v>S18/2026/071</v>
       </c>
       <c r="D28" t="str">
-        <v>23/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="E28">
-        <v>74340</v>
+        <v>164020</v>
       </c>
       <c r="F28">
-        <v>63000</v>
+        <v>139000</v>
       </c>
       <c r="G28">
-        <v>11340</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>12510</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>12510</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>2026-05</v>
       </c>
       <c r="L28" t="str">
-        <v>16/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="M28" t="str">
         <v>Yes</v>
@@ -1545,31 +1545,31 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>09AAHFG4423Y1ZH</v>
+        <v>27AAKFP6678U1ZU</v>
       </c>
       <c r="B29" t="str">
-        <v>Ganga Textiles</v>
+        <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C29" t="str">
-        <v>S17/2026/071</v>
+        <v>S18/2026/072</v>
       </c>
       <c r="D29" t="str">
-        <v>17/04/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="E29">
-        <v>61360</v>
+        <v>166380</v>
       </c>
       <c r="F29">
-        <v>52000</v>
+        <v>141000</v>
       </c>
       <c r="G29">
-        <v>9360</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>12690</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>12690</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>2026-05</v>
       </c>
       <c r="L29" t="str">
-        <v>12/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="M29" t="str">
         <v>Yes</v>
@@ -1598,25 +1598,25 @@
         <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C30" t="str">
-        <v>S18/2026/071</v>
+        <v>S18/2026/073</v>
       </c>
       <c r="D30" t="str">
-        <v>11/04/2026</v>
+        <v>14/04/2026</v>
       </c>
       <c r="E30">
-        <v>149860</v>
+        <v>165200</v>
       </c>
       <c r="F30">
-        <v>127000</v>
+        <v>140000</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>11430</v>
+        <v>12600</v>
       </c>
       <c r="I30">
-        <v>11430</v>
+        <v>12600</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>2026-05</v>
       </c>
       <c r="L30" t="str">
-        <v>14/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="M30" t="str">
         <v>Yes</v>
@@ -1639,31 +1639,31 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B31" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C31" t="str">
-        <v>S18/2026/072</v>
+        <v>S19/2026/071</v>
       </c>
       <c r="D31" t="str">
-        <v>19/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="E31">
-        <v>172280</v>
+        <v>118000</v>
       </c>
       <c r="F31">
-        <v>146000</v>
+        <v>100000</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="H31">
-        <v>13140</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>13140</v>
+        <v>0</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>2026-05</v>
       </c>
       <c r="L31" t="str">
-        <v>15/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="M31" t="str">
         <v>Yes</v>
@@ -1686,31 +1686,31 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B32" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C32" t="str">
-        <v>S18/2026/073</v>
+        <v>S19/2026/072</v>
       </c>
       <c r="D32" t="str">
-        <v>17/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="E32">
-        <v>162840</v>
+        <v>92040</v>
       </c>
       <c r="F32">
-        <v>138000</v>
+        <v>78000</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>14040</v>
       </c>
       <c r="H32">
-        <v>12420</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>12420</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -1719,7 +1719,7 @@
         <v>2026-05</v>
       </c>
       <c r="L32" t="str">
-        <v>14/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="M32" t="str">
         <v>Yes</v>
@@ -1733,31 +1733,31 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>33AABFS2234V1ZT</v>
+        <v>27AAFCA8801X1ZT</v>
       </c>
       <c r="B33" t="str">
-        <v>Sundar Printing Works</v>
+        <v>Ashoka Civil Works</v>
       </c>
       <c r="C33" t="str">
-        <v>S19/2026/071</v>
+        <v>S20/2026/072</v>
       </c>
       <c r="D33" t="str">
-        <v>26/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="E33">
-        <v>116820</v>
+        <v>147500</v>
       </c>
       <c r="F33">
-        <v>99000</v>
+        <v>125000</v>
       </c>
       <c r="G33">
-        <v>17820</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>11250</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>11250</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>2026-05</v>
       </c>
       <c r="L33" t="str">
-        <v>09/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="M33" t="str">
         <v>Yes</v>
@@ -1780,25 +1780,25 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>33AABFS2234V1ZT</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B34" t="str">
-        <v>Sundar Printing Works</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C34" t="str">
-        <v>S19/2026/072</v>
+        <v>S21/2026/061</v>
       </c>
       <c r="D34" t="str">
-        <v>05/04/2026</v>
+        <v>08/03/2026</v>
       </c>
       <c r="E34">
-        <v>101480</v>
+        <v>187620</v>
       </c>
       <c r="F34">
-        <v>86000</v>
+        <v>159000</v>
       </c>
       <c r="G34">
-        <v>15480</v>
+        <v>28620</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -1827,31 +1827,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B35" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C35" t="str">
-        <v>S20/2026/071</v>
+        <v>S21/2026/071</v>
       </c>
       <c r="D35" t="str">
-        <v>05/04/2026</v>
+        <v>22/04/2026</v>
       </c>
       <c r="E35">
-        <v>154580</v>
+        <v>204140</v>
       </c>
       <c r="F35">
-        <v>131000</v>
+        <v>173000</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>31140</v>
       </c>
       <c r="H35">
-        <v>11790</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>11790</v>
+        <v>0</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>2026-05</v>
       </c>
       <c r="L35" t="str">
-        <v>13/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="M35" t="str">
         <v>Yes</v>
@@ -1874,31 +1874,31 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B36" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C36" t="str">
-        <v>S20/2026/072</v>
+        <v>S21/2026/072</v>
       </c>
       <c r="D36" t="str">
-        <v>13/04/2026</v>
+        <v>06/04/2026</v>
       </c>
       <c r="E36">
-        <v>151040</v>
+        <v>187620</v>
       </c>
       <c r="F36">
-        <v>128000</v>
+        <v>159000</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>28620</v>
       </c>
       <c r="H36">
-        <v>11520</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>11520</v>
+        <v>0</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1907,7 +1907,7 @@
         <v>2026-05</v>
       </c>
       <c r="L36" t="str">
-        <v>14/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="M36" t="str">
         <v>Yes</v>
@@ -1927,19 +1927,19 @@
         <v>Nova Instruments</v>
       </c>
       <c r="C37" t="str">
-        <v>S21/2026/071</v>
+        <v>S21/2026/073</v>
       </c>
       <c r="D37" t="str">
-        <v>16/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="E37">
-        <v>206500</v>
+        <v>204140</v>
       </c>
       <c r="F37">
-        <v>175000</v>
+        <v>173000</v>
       </c>
       <c r="G37">
-        <v>31500</v>
+        <v>31140</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>2026-05</v>
       </c>
       <c r="L37" t="str">
-        <v>15/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="M37" t="str">
         <v>Yes</v>
@@ -1968,31 +1968,31 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>27AAGFM1167A1ZO</v>
       </c>
       <c r="B38" t="str">
-        <v>Nova Instruments</v>
+        <v>Meridian Housekeeping</v>
       </c>
       <c r="C38" t="str">
-        <v>S21/2026/073</v>
+        <v>S22/2026/071</v>
       </c>
       <c r="D38" t="str">
-        <v>15/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="E38">
-        <v>206500</v>
+        <v>210040</v>
       </c>
       <c r="F38">
-        <v>175000</v>
+        <v>178000</v>
       </c>
       <c r="G38">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>16020</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>16020</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>2026-05</v>
       </c>
       <c r="L38" t="str">
-        <v>16/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="M38" t="str">
         <v>Yes</v>
@@ -2015,31 +2015,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>27AAGFM1167A1ZO</v>
+        <v>24AAECC7789B1ZM</v>
       </c>
       <c r="B39" t="str">
-        <v>Meridian Housekeeping</v>
+        <v>Coral Adhesives</v>
       </c>
       <c r="C39" t="str">
-        <v>S22/2026/071</v>
+        <v>S23/2026/071</v>
       </c>
       <c r="D39" t="str">
-        <v>07/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="E39">
-        <v>192340</v>
+        <v>186440</v>
       </c>
       <c r="F39">
-        <v>163000</v>
+        <v>158000</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>28440</v>
       </c>
       <c r="H39">
-        <v>14670</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>14670</v>
+        <v>0</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>2026-05</v>
       </c>
       <c r="L39" t="str">
-        <v>12/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="M39" t="str">
         <v>Yes</v>
@@ -2071,16 +2071,16 @@
         <v>S24/2026/071</v>
       </c>
       <c r="D40" t="str">
-        <v>23/04/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="E40">
-        <v>155760</v>
+        <v>146320</v>
       </c>
       <c r="F40">
-        <v>132000</v>
+        <v>124000</v>
       </c>
       <c r="G40">
-        <v>23760</v>
+        <v>22320</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>2026-05</v>
       </c>
       <c r="L40" t="str">
-        <v>08/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="M40" t="str">
         <v>Yes</v>
@@ -2118,16 +2118,16 @@
         <v>S24/2026/072</v>
       </c>
       <c r="D41" t="str">
-        <v>13/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="E41">
-        <v>165200</v>
+        <v>153400</v>
       </c>
       <c r="F41">
-        <v>140000</v>
+        <v>130000</v>
       </c>
       <c r="G41">
-        <v>25200</v>
+        <v>23400</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>2026-05</v>
       </c>
       <c r="L41" t="str">
-        <v>10/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="M41" t="str">
         <v>Yes</v>
@@ -2165,16 +2165,16 @@
         <v>S24/2026/073</v>
       </c>
       <c r="D42" t="str">
-        <v>06/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="E42">
-        <v>152220</v>
+        <v>142780</v>
       </c>
       <c r="F42">
-        <v>129000</v>
+        <v>121000</v>
       </c>
       <c r="G42">
-        <v>23220</v>
+        <v>21780</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>2026-05</v>
       </c>
       <c r="L42" t="str">
-        <v>16/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="M42" t="str">
         <v>Yes</v>
@@ -2212,22 +2212,22 @@
         <v>S25/2026/071</v>
       </c>
       <c r="D43" t="str">
-        <v>04/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="E43">
-        <v>35400</v>
+        <v>40120</v>
       </c>
       <c r="F43">
-        <v>30000</v>
+        <v>34000</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>2700</v>
+        <v>3060</v>
       </c>
       <c r="I43">
-        <v>2700</v>
+        <v>3060</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>2026-05</v>
       </c>
       <c r="L43" t="str">
-        <v>15/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="M43" t="str">
         <v>Yes</v>
